--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M8B2_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M8B2_IN_Piura.xlsx
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>14.77</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C11" s="30">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>54.01</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>26.49</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>4.65</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.08</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1924,11 +1924,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>35.3471</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1949,11 +1949,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>24.3106</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>68.78</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1974,11 +1974,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>11.0365</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>31.22</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2172,11 +2172,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>35.3633</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2295,6 +2295,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2445,6 +2446,7 @@
       <c r="F13" s="17" t="inlineStr"/>
       <c r="G13" s="17" t="inlineStr"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2489,6 +2491,7 @@
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="96" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
@@ -2708,11 +2711,11 @@
       </c>
       <c r="B12" s="32">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>365.95</v>
       </c>
       <c r="C12" s="23">
         <f>SUM(C10:C11)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -2722,19 +2725,19 @@
       <c r="E12" s="17" t="inlineStr"/>
       <c r="F12" s="17">
         <f>ROUND(AVERAGE(F10:F11),2)</f>
-        <v/>
+        <v>18.88</v>
       </c>
       <c r="G12" s="22">
         <f>ROUND(AVERAGE(G10:G11),4)</f>
-        <v/>
+        <v>0.4446</v>
       </c>
       <c r="H12" s="23">
         <f>ROUND(AVERAGE(H10:H11),2)</f>
-        <v/>
+        <v>29.95</v>
       </c>
       <c r="I12" s="23">
         <f>ROUND(AVERAGE(I10:I11),2)</f>
-        <v/>
+        <v>65.2</v>
       </c>
     </row>
     <row r="13"/>
